--- a/wiki/金融投資/台灣ETF比較清單.xlsx
+++ b/wiki/金融投資/台灣ETF比較清單.xlsx
@@ -36,12 +36,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -56,8 +62,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -3686,7 +3693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3842,6 +3849,43 @@
       <c r="G4" t="inlineStr">
         <is>
           <t>0.15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>00685L</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>群益臺灣加權正2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>臺灣加權指數 (單日2倍)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>洪祥益</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>玉山銀行</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.30%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.04%</t>
         </is>
       </c>
     </row>

--- a/wiki/金融投資/台灣ETF比較清單.xlsx
+++ b/wiki/金融投資/台灣ETF比較清單.xlsx
@@ -56,10 +56,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="1" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -3902,10 +3901,9 @@
     <col width="29" bestFit="1" customWidth="1" min="2" max="2"/>
     <col width="33.85546875" bestFit="1" customWidth="1" min="3" max="3"/>
     <col width="8.140625" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="10.28515625" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="15.140625" bestFit="1" customWidth="1" min="5" max="5"/>
     <col width="15.28515625" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="15" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="19.7109375" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="20.85546875" bestFit="1" customWidth="1" min="7" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4351,7 +4349,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>第一商業銀行</t>
+          <t>中國信託商業銀行</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -4361,12 +4359,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>0.80%</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>0.06%~0.12% (級距)</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.035%</t>
         </is>
       </c>
     </row>

--- a/wiki/金融投資/台灣ETF比較清單.xlsx
+++ b/wiki/金融投資/台灣ETF比較清單.xlsx
@@ -20,13 +20,21 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="新細明體"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="1"/>
+      <color rgb="FF0563C1"/>
+      <sz val="11"/>
+      <u val="single"/>
     </font>
     <font>
       <name val="新細明體"/>
@@ -58,7 +66,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="1" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -424,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -732,27 +740,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00980A</t>
+          <t>00407A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>野村臺灣智慧優選</t>
+          <t>凱基台灣主動式</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>游景德</t>
+          <t>趙偉志</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>華南銀行</t>
+          <t>彰化銀行</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>季配 (2,5,8,11)</t>
+          <t>不配息</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -767,254 +775,254 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026/05/19</t>
+          <t>不配息</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>統一台股增長</t>
+          <t>野村臺灣智慧優選</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>陳釧瑤</t>
+          <t>游景德</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>彰化銀行</t>
+          <t>華南銀行</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>季配 (3,6,9,12)</t>
+          <t>季配 (2,5,8,11)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.0%~1.2%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.10%~0.12%</t>
+          <t>0.035%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026/03/17</t>
+          <t>2026/05/19</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>群益台灣精選強棒</t>
+          <t>統一台股增長</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>陳沅易</t>
+          <t>陳釧瑤</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>中國信託</t>
+          <t>彰化銀行</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>季配 (2,5,8,11)</t>
+          <t>季配 (3,6,9,12)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>1.0%~1.2%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.035%</t>
+          <t>0.10%~0.12%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026/05/19</t>
+          <t>2026/03/17</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>00983A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>中信ARK創新</t>
+          <t>群益台灣精選強棒</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>唐祖蔭</t>
+          <t>陳沅易</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>第一銀行</t>
+          <t>中國信託</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>年配 (12)</t>
+          <t>季配 (2,5,8,11)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.7%~1.0%</t>
+          <t>0.80%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.12%~0.15%</t>
+          <t>0.035%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>尚未公告</t>
+          <t>2026/05/19</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>00984A</t>
+          <t>00983A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>安聯台灣高息成長</t>
+          <t>中信ARK創新</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>廖本隆</t>
+          <t>唐祖蔭</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>國泰世華</t>
+          <t>第一銀行</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>季配 (1,4,7,10)</t>
+          <t>年配 (12)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.7%~1.0%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.12%~0.15%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026/04/20</t>
+          <t>尚未公告</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00984A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>野村臺灣增強50</t>
+          <t>安聯台灣高息成長</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>林浩詳</t>
+          <t>廖本隆</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>台北富邦</t>
+          <t>國泰世華</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>年配 (12)</t>
+          <t>季配 (1,4,7,10)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.70%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.035%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>尚未公告</t>
+          <t>2026/04/20</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>00986A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>台新全球龍頭成長</t>
+          <t>野村臺灣增強50</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>蘇聖峰</t>
+          <t>林浩詳</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>臺灣企銀</t>
+          <t>台北富邦</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>年配 (10)</t>
+          <t>年配 (12)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.035%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1026,37 +1034,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>00987A</t>
+          <t>00986A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>台新優勢成長</t>
+          <t>台新全球龍頭成長</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>魏永祥</t>
+          <t>蘇聖峰</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>彰化銀行</t>
+          <t>臺灣企銀</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>年配 (11)</t>
+          <t>年配 (10)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.25%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1068,37 +1076,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>00988A</t>
+          <t>00987A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>統一全球創新</t>
+          <t>台新優勢成長</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>陳意婷</t>
+          <t>魏永祥</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>元大銀行</t>
+          <t>彰化銀行</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>年配 (9)</t>
+          <t>年配 (11)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1.2%~1.4%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.10%~0.12%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1110,37 +1118,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>00989A</t>
+          <t>00988A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>摩根大美國領先科技</t>
+          <t>統一全球創新</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>蓋欣聖</t>
+          <t>陳意婷</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>中國信託</t>
+          <t>元大銀行</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>季配 (1,4,7,10)</t>
+          <t>年配 (10)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>1.2%~1.4%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.15%</t>
+          <t>0.10%~0.12%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1152,32 +1160,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00989A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>元大AI新經濟</t>
+          <t>摩根大美國領先科技</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>吳昭豪</t>
+          <t>蓋欣聖</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>臺灣銀行</t>
+          <t>中國信託</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>不配息</t>
+          <t>季配 (1,4,7,10)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1187,66 +1195,66 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>不配息</t>
+          <t>尚未公告</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>復華台灣未來50</t>
+          <t>元大AI新經濟</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>呂宏宇</t>
+          <t>吳昭豪</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>第一銀行</t>
+          <t>臺灣銀行</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>半年配 (1,7)</t>
+          <t>不配息</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.80%~1.0%</t>
+          <t>0.90%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.035%~0.04%</t>
+          <t>0.15%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>尚未公告</t>
+          <t>不配息</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>群益科技創新</t>
+          <t>復華台灣未來50</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>陳朝政</t>
+          <t>呂宏宇</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1256,17 +1264,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>季配 (1,4,7,10)</t>
+          <t>半年配 (1,7)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.0%~1.2%</t>
+          <t>0.80%~1.0%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.035%~0.04%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1278,32 +1286,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>安聯台灣主動</t>
+          <t>群益科技創新</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>施政廷</t>
+          <t>陳朝政</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>中國信託</t>
+          <t>第一銀行</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>年配 (12)</t>
+          <t>季配 (1,4,7,10)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>1.0%~1.2%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1320,37 +1328,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>00994A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>第一金台股優</t>
+          <t>安聯台灣主動</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>張正中</t>
+          <t>施政廷</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>永豐商業銀行</t>
+          <t>中國信託</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>季配 (3,6,9,12)</t>
+          <t>年配 (12)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.80%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.035%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1362,37 +1370,37 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>00995A</t>
+          <t>00994A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>中信台灣卓越成長</t>
+          <t>第一金台股優</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>張書廷</t>
+          <t>張正中</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>元大銀行</t>
+          <t>永豐商業銀行</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>季配 (1,4,7,10)</t>
+          <t>季配 (3,6,9,12)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.70%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.035%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1404,17 +1412,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>00996A</t>
+          <t>00995A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>兆豐台灣豐收</t>
+          <t>中信台灣卓越成長</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>王仲良</t>
+          <t>張書廷</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1429,7 +1437,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1446,22 +1454,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>00997A</t>
+          <t>00996A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>群益美國增長</t>
+          <t>兆豐台灣豐收</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>吳承恕</t>
+          <t>王仲良</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>第一銀行</t>
+          <t>元大銀行</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1471,12 +1479,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.0%~1.2%</t>
+          <t>0.80%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.1%~0.12%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1488,27 +1496,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>00998A</t>
+          <t>00997A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>復華全球金融入息</t>
+          <t>群益美國增長</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>張正宇</t>
+          <t>吳承恕</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>合作金庫</t>
+          <t>第一銀行</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>季配 (3,6,9,12)</t>
+          <t>季配 (1,4,7,10)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1518,7 +1526,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.10%~0.14%</t>
+          <t>0.1%~0.12%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1530,22 +1538,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>00999A</t>
+          <t>00998A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>野村臺灣策略高息</t>
+          <t>復華全球金融入息</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>游景德</t>
+          <t>張正宇</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>第一銀行</t>
+          <t>合作金庫</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1555,12 +1563,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>1.0%~1.2%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.035%</t>
+          <t>0.10%~0.14%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1572,82 +1580,124 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>00980D</t>
+          <t>00999A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>聯博投等債入息</t>
+          <t>野村臺灣策略高息</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>陳俊憲</t>
+          <t>游景德</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>中國信託</t>
+          <t>第一銀行</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>月配</t>
+          <t>季配 (3,6,9,12)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.60%~0.65%</t>
+          <t>0.70%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.08%~0.12%</t>
+          <t>0.035%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026/05/19</t>
+          <t>尚未公告</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>00980D</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>聯博投等債入息</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>陳俊憲</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>中國信託</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>月配</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>0.60%~0.65%</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0.08%~0.12%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026/05/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>00983D</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>富邦複合收益</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>游陳達</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>第一銀行</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>月配</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>0.55%~0.65%</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>0.06%~0.10%</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>2026/05/19</t>
         </is>
@@ -1655,7 +1705,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -1668,14 +1717,13 @@
   <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
-    <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="20" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="8.140625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="10.28515625" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="29.42578125" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="17.42578125" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="15" bestFit="1" customWidth="1" min="7" max="8"/>
-    <col width="15.140625" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="6"/>
+    <col width="13" customWidth="1" min="7" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1726,7 +1774,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>0050</t>
         </is>
@@ -1773,7 +1821,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>0052</t>
         </is>
@@ -1820,7 +1868,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>006204</t>
         </is>
@@ -1867,7 +1915,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>006208</t>
         </is>
@@ -1914,7 +1962,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>00692</t>
         </is>
@@ -1961,7 +2009,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>00733</t>
         </is>
@@ -2008,7 +2056,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>00850</t>
         </is>
@@ -2055,7 +2103,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>00881</t>
         </is>
@@ -2102,7 +2150,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>00888</t>
         </is>
@@ -2149,7 +2197,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>00905</t>
         </is>
@@ -2196,7 +2244,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>00912</t>
         </is>
@@ -2243,7 +2291,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>00913</t>
         </is>
@@ -2290,7 +2338,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>00921</t>
         </is>
@@ -2337,7 +2385,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>00922</t>
         </is>
@@ -2384,7 +2432,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>00923</t>
         </is>
@@ -2431,7 +2479,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>00935</t>
         </is>
@@ -2478,7 +2526,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>00947</t>
         </is>
@@ -2525,7 +2573,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>009804</t>
         </is>
@@ -2572,7 +2620,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>009816</t>
         </is>
@@ -2619,6 +2667,27 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2630,16 +2699,16 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I22"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="7.140625" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
-    <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="24.7109375" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="10.28515625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="15.140625" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="31.85546875" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="22.28515625" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="15" bestFit="1" customWidth="1" min="7" max="8"/>
-    <col width="15.140625" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2690,7 +2759,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>0056</t>
         </is>
@@ -2737,7 +2806,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>00701</t>
         </is>
@@ -2784,7 +2853,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>00713</t>
         </is>
@@ -2831,7 +2900,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>00730</t>
         </is>
@@ -2878,7 +2947,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>00731</t>
         </is>
@@ -2925,7 +2994,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>00878</t>
         </is>
@@ -2972,7 +3041,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>00900</t>
         </is>
@@ -3019,7 +3088,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>00907</t>
         </is>
@@ -3066,7 +3135,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>00915</t>
         </is>
@@ -3113,7 +3182,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>00918</t>
         </is>
@@ -3160,7 +3229,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>00919</t>
         </is>
@@ -3207,7 +3276,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>00929</t>
         </is>
@@ -3254,7 +3323,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>00930</t>
         </is>
@@ -3301,7 +3370,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>00934</t>
         </is>
@@ -3348,7 +3417,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>00936</t>
         </is>
@@ -3395,7 +3464,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>00939</t>
         </is>
@@ -3442,7 +3511,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>00940</t>
         </is>
@@ -3489,7 +3558,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>00944</t>
         </is>
@@ -3536,7 +3605,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>00946</t>
         </is>
@@ -3583,7 +3652,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>00961</t>
         </is>
@@ -3630,7 +3699,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>00964</t>
         </is>
@@ -3677,6 +3746,29 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3687,12 +3779,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="18.7109375" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="25.7109375" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="30.42578125" bestFit="1" customWidth="1" min="3" max="3"/>
     <col width="8.140625" bestFit="1" customWidth="1" min="4" max="4"/>
     <col width="10.28515625" bestFit="1" customWidth="1" min="5" max="5"/>
     <col width="15" bestFit="1" customWidth="1" min="6" max="7"/>
@@ -3736,7 +3828,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>00631L</t>
         </is>
@@ -3773,7 +3865,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>00632R</t>
         </is>
@@ -3810,80 +3902,352 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>00647L</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>元大S&amp;P500正2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>S&amp;P500指數 (單日2倍)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>方雅婷</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>玉山銀行</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0.99%</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>00648R</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>元大S&amp;P500反1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>S&amp;P500指數 (單日-1倍)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>方雅婷</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>玉山銀行</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.99%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.18%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>00663L</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>國泰臺灣加權正2</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>臺灣加權指數 (單日2倍)</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>蘇鼎宇</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>國泰世華</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>0.75%</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>0.15%</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>00664R</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>國泰臺灣加權反1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>臺灣加權指數 (單日-1倍)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>蘇鼎宇</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>玉山銀行</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0.75%</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.04%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>00670L</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>富邦NASDAQ正2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NASDAQ-100指數 (單日2倍)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>陳婉寧</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>中國信託</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0.89%</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>00671R</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>富邦NASDAQ反1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NASDAQ-100指數 (單日-1倍)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>蘇筱婷</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>中國信託</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0.89%</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.18%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>00675L</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>富邦臺灣加權正2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>臺灣加權指數 (單日2倍)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>林威宇</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>華南銀行</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0.65%</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.04%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>00685L</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>群益臺灣加權正2</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>臺灣加權指數 (單日2倍)</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>洪祥益</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>玉山銀行</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>0.30%</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>0.04%</t>
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>00686R</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>群益臺灣加權反1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>臺灣加權指數 (單日-1倍)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>洪祥益</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>玉山銀行</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0.30%</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.04%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3895,15 +4259,16 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="15.75"/>
   <cols>
     <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
     <col width="29" bestFit="1" customWidth="1" min="2" max="2"/>
     <col width="33.85546875" bestFit="1" customWidth="1" min="3" max="3"/>
     <col width="8.140625" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="15.140625" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="20" bestFit="1" customWidth="1" min="5" max="5"/>
     <col width="15.28515625" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="20.85546875" bestFit="1" customWidth="1" min="7" max="8"/>
+    <col width="15" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="20.85546875" bestFit="1" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3949,7 +4314,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>00646</t>
         </is>
@@ -3991,7 +4356,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>00662</t>
         </is>
@@ -4033,7 +4398,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>00712</t>
         </is>
@@ -4075,7 +4440,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>00757</t>
         </is>
@@ -4117,7 +4482,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>00770</t>
         </is>
@@ -4159,7 +4524,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>00830</t>
         </is>
@@ -4201,7 +4566,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>00924</t>
         </is>
@@ -4243,7 +4608,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>00941</t>
         </is>
@@ -4369,6 +4734,18 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/wiki/金融投資/台灣ETF比較清單.xlsx
+++ b/wiki/金融投資/台灣ETF比較清單.xlsx
@@ -1714,7 +1714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2662,6 +2662,53 @@
         </is>
       </c>
       <c r="I20" t="inlineStr">
+        <is>
+          <t>不配息</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>009821</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>野村全球稀土與關鍵資源</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>張怡琳</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>永豐商業銀行</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>NYSE TIP全球稀土與關鍵資源指數</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>不配息</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0.90%</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>不配息</t>
         </is>

--- a/wiki/金融投資/台灣ETF比較清單.xlsx
+++ b/wiki/金融投資/台灣ETF比較清單.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="海外型" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'主動型'!$A$1:$H$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'主動型'!$A$1:$H$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'市值型'!$A$1:$I$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'高股息'!$A$1:$I$22</definedName>
   </definedNames>
@@ -68,9 +68,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="1" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -436,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -527,7 +528,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>尚未公告</t>
+          <t>2026/07/08</t>
         </is>
       </c>
     </row>
@@ -786,27 +787,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>00980A</t>
+          <t>00408A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>野村臺灣智慧優選</t>
+          <t>主動第一金優股息</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>游景德</t>
+          <t>張正中</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>華南銀行</t>
+          <t>臺灣中小企業銀行</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>季配 (2,5,8,11)</t>
+          <t>季配 (1,4,7,10)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -821,254 +822,254 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026/05/19</t>
+          <t>尚未公告</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>統一台股增長</t>
+          <t>野村臺灣智慧優選</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>陳釧瑤</t>
+          <t>游景德</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>彰化銀行</t>
+          <t>華南銀行</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>季配 (3,6,9,12)</t>
+          <t>季配 (2,5,8,11)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.0%~1.2%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.10%~0.12%</t>
+          <t>0.035%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026/03/17</t>
+          <t>2026/05/18</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>群益台灣精選強棒</t>
+          <t>統一台股增長</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>陳沅易</t>
+          <t>陳釧瑤</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>中國信託</t>
+          <t>彰化銀行</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>季配 (2,5,8,11)</t>
+          <t>季配 (3,6,9,12)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>1.0%~1.2%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.035%</t>
+          <t>0.10%~0.12%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026/05/19</t>
+          <t>2026/06/15</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>00983A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>中信ARK創新</t>
+          <t>群益台灣精選強棒</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>唐祖蔭</t>
+          <t>陳沅易</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>第一銀行</t>
+          <t>中國信託</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>年配 (12)</t>
+          <t>季配 (2,5,8,11)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.7%~1.0%</t>
+          <t>0.80%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.12%~0.15%</t>
+          <t>0.035%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>尚未公告</t>
+          <t>2026/05/18</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>00984A</t>
+          <t>00983A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>安聯台灣高息成長</t>
+          <t>中信ARK創新</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>廖本隆</t>
+          <t>唐祖蔭</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>國泰世華</t>
+          <t>第一銀行</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>季配 (1,4,7,10)</t>
+          <t>年配 (12)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.7%~1.0%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.12%~0.15%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026/04/20</t>
+          <t>尚未公告</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00984A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>野村臺灣增強50</t>
+          <t>安聯台灣高息成長</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>林浩詳</t>
+          <t>廖本隆</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>台北富邦</t>
+          <t>國泰世華</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>年配 (12)</t>
+          <t>季配 (1,4,7,10)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.70%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.035%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>尚未公告</t>
+          <t>2026/07/15</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>00986A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>台新全球龍頭成長</t>
+          <t>野村臺灣增強50</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>蘇聖峰</t>
+          <t>林浩詳</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>臺灣企銀</t>
+          <t>台北富邦</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>年配 (10)</t>
+          <t>年配 (12)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.035%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1080,37 +1081,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>00987A</t>
+          <t>00986A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>台新優勢成長</t>
+          <t>台新全球龍頭成長</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>魏永祥</t>
+          <t>蘇聖峰</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>彰化銀行</t>
+          <t>臺灣企銀</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>年配 (11)</t>
+          <t>年配 (10)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.25%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1122,37 +1123,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>00988A</t>
+          <t>00987A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>統一全球創新</t>
+          <t>台新優勢成長</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>陳意婷</t>
+          <t>魏永祥</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>元大銀行</t>
+          <t>彰化銀行</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>年配 (10)</t>
+          <t>年配 (11)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1.2%~1.4%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.10%~0.12%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1164,37 +1165,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>00989A</t>
+          <t>00988A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>摩根大美國領先科技</t>
+          <t>統一全球創新</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>蓋欣聖</t>
+          <t>陳意婷</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>中國信託</t>
+          <t>元大銀行</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>季配 (1,4,7,10)</t>
+          <t>年配 (10)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>1.2%~1.4%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.15%</t>
+          <t>0.10%~0.12%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1206,32 +1207,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00989A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>元大AI新經濟</t>
+          <t>摩根大美國領先科技</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>吳昭豪</t>
+          <t>蓋欣聖</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>臺灣銀行</t>
+          <t>中國信託</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>不配息</t>
+          <t>季配 (1,4,7,10)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1241,66 +1242,66 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>不配息</t>
+          <t>尚未公告</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>00991A</t>
+          <t>00990A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>復華台灣未來50</t>
+          <t>元大AI新經濟</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>呂宏宇</t>
+          <t>吳昭豪</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>第一銀行</t>
+          <t>臺灣銀行</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>半年配 (1,7)</t>
+          <t>不配息</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.80%~1.0%</t>
+          <t>0.90%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.035%~0.04%</t>
+          <t>0.15%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>尚未公告</t>
+          <t>不配息</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>群益科技創新</t>
+          <t>復華台灣未來50</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>陳朝政</t>
+          <t>呂宏宇</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1310,54 +1311,54 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>季配 (1,4,7,10)</t>
+          <t>半年配 (1,7)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.0%~1.2%</t>
+          <t>0.80%~1.0%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.035%~0.04%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>尚未公告</t>
+          <t>2026/07/20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>00993A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>安聯台灣主動</t>
+          <t>群益科技創新</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>施政廷</t>
+          <t>陳朝政</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>中國信託</t>
+          <t>第一銀行</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>年配 (12)</t>
+          <t>季配 (1,4,7,10)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>1.0%~1.2%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1367,44 +1368,44 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>尚未公告</t>
+          <t>2026/07/15</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>00994A</t>
+          <t>00993A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>第一金台股優</t>
+          <t>安聯台灣主動</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>張正中</t>
+          <t>施政廷</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>永豐商業銀行</t>
+          <t>中國信託</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>季配 (3,6,9,12)</t>
+          <t>年配 (12)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.80%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.035%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1416,59 +1417,59 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>00995A</t>
+          <t>00994A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>中信台灣卓越成長</t>
+          <t>第一金台股優</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>張書廷</t>
+          <t>張正中</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>元大銀行</t>
+          <t>永豐商業銀行</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>季配 (1,4,7,10)</t>
+          <t>季配 (3,6,9,12)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.70%</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.035%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>尚未公告</t>
+          <t>2026/06/17</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>00996A</t>
+          <t>00995A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>兆豐台灣豐收</t>
+          <t>中信台灣卓越成長</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>王仲良</t>
+          <t>張書廷</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1483,7 +1484,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1500,22 +1501,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>00997A</t>
+          <t>00996A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>群益美國增長</t>
+          <t>兆豐台灣豐收</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>吳承恕</t>
+          <t>王仲良</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>第一銀行</t>
+          <t>元大銀行</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1525,12 +1526,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1.0%~1.2%</t>
+          <t>0.80%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.1%~0.12%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1542,27 +1543,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>00998A</t>
+          <t>00997A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>復華全球金融入息</t>
+          <t>群益美國增長</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>張正宇</t>
+          <t>吳承恕</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>合作金庫</t>
+          <t>第一銀行</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>季配 (3,6,9,12)</t>
+          <t>季配 (1,4,7,10)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1572,34 +1573,34 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.10%~0.14%</t>
+          <t>0.1%~0.12%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>尚未公告</t>
+          <t>2026/07/03</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>00999A</t>
+          <t>00998A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>野村臺灣策略高息</t>
+          <t>復華全球金融入息</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>游景德</t>
+          <t>張正宇</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>第一銀行</t>
+          <t>合作金庫</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1609,106 +1610,148 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>1.0%~1.2%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.035%</t>
+          <t>0.10%~0.14%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>尚未公告</t>
+          <t>2026/06/16</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>00980D</t>
+          <t>00999A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>聯博投等債入息</t>
+          <t>野村臺灣策略高息</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>陳俊憲</t>
+          <t>游景德</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>中國信託</t>
+          <t>第一銀行</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>月配</t>
+          <t>季配 (3,6,9,12)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.60%~0.65%</t>
+          <t>0.70%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.08%~0.12%</t>
+          <t>0.035%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026/05/19</t>
+          <t>尚未公告</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>00980D</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>聯博投等債入息</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>陳俊憲</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>中國信託</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>月配</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>0.60%~0.65%</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>0.08%~0.12%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026/07/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>00983D</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>富邦複合收益</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>游陳達</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>第一銀行</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>月配</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>0.55%~0.65%</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>0.06%~0.10%</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>2026/05/19</t>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2026/07/15</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H30"/>
+  <autoFilter ref="A1:H31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1719,7 +1762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1822,7 +1865,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026/01/22</t>
+          <t>2026/07/20</t>
         </is>
       </c>
     </row>
@@ -1916,7 +1959,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026/01/21</t>
+          <t>2025/10/22</t>
         </is>
       </c>
     </row>
@@ -1963,7 +2006,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2025/11/18</t>
+          <t>2026/07/15</t>
         </is>
       </c>
     </row>
@@ -2010,7 +2053,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2025/11/18</t>
+          <t>2026/07/15</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2100,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026/04/20</t>
+          <t>2026/04/17</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2147,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026/05/22</t>
+          <t>2026/05/21</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2194,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026/01/20</t>
+          <t>2026/01/19</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2241,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026/04/23</t>
+          <t>2026/07/24</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2288,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026/04/20</t>
+          <t>2026/07/15</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2335,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026/04/20</t>
+          <t>2026/07/15</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2429,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026/03/18</t>
+          <t>2026/06/15</t>
         </is>
       </c>
     </row>
@@ -2433,7 +2476,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026/03/17</t>
+          <t>2026/03/16</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2523,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026/02/26</t>
+          <t>2026/02/25</t>
         </is>
       </c>
     </row>
@@ -2527,7 +2570,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026/03/18</t>
+          <t>2026/03/16</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2617,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026/04/20</t>
+          <t>2026/07/14</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2664,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026/04/17</t>
+          <t>2026/07/15</t>
         </is>
       </c>
     </row>
@@ -2716,6 +2759,13 @@
       <c r="I21" t="inlineStr">
         <is>
           <t>不配息</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>009826</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2906,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026/04/17</t>
+          <t>2026/07/20</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2953,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026/01/21</t>
+          <t>2026/01/19</t>
         </is>
       </c>
     </row>
@@ -2950,7 +3000,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026/03/18</t>
+          <t>2026/06/18</t>
         </is>
       </c>
     </row>
@@ -2997,7 +3047,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026/05/19</t>
+          <t>2026/07/15</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3094,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/05/19</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3141,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026/05/19</t>
+          <t>2026/05/18</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3188,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026/05/19</t>
+          <t>2026/07/15</t>
         </is>
       </c>
     </row>
@@ -3185,7 +3235,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026/04/23</t>
+          <t>2026/06/23</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3282,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026/03/18</t>
+          <t>2026/06/15</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3329,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026/03/18</t>
+          <t>2026/06/17</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3376,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026/03/18</t>
+          <t>2026/06/15</t>
         </is>
       </c>
     </row>
@@ -3373,7 +3423,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/07/20</t>
         </is>
       </c>
     </row>
@@ -3420,7 +3470,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026/05/26</t>
+          <t>2026/07/24</t>
         </is>
       </c>
     </row>
@@ -3467,7 +3517,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026/05/19</t>
+          <t>2026/07/15</t>
         </is>
       </c>
     </row>
@@ -3514,7 +3564,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026/05/18</t>
+          <t>2026/07/14</t>
         </is>
       </c>
     </row>
@@ -3561,7 +3611,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026/05/04</t>
+          <t>2026/07/01</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3658,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026/05/20</t>
+          <t>2026/07/08</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3705,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026/05/19</t>
+          <t>2026/07/15</t>
         </is>
       </c>
     </row>
@@ -3702,7 +3752,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026/05/06</t>
+          <t>2026/07/03</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3799,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026/05/19</t>
+          <t>2026/07/15</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3846,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026/05/19</t>
+          <t>2026/07/15</t>
         </is>
       </c>
     </row>

--- a/wiki/金融投資/台灣ETF比較清單.xlsx
+++ b/wiki/金融投資/台灣ETF比較清單.xlsx
@@ -1762,7 +1762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2759,13 +2759,6 @@
       <c r="I21" t="inlineStr">
         <is>
           <t>不配息</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>009826</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="15.75"/>
   <cols>
     <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -4836,6 +4829,13 @@
       <c r="H11" t="inlineStr">
         <is>
           <t>0.06%~0.12% (級距)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>009826</t>
         </is>
       </c>
     </row>

--- a/wiki/金融投資/台灣ETF比較清單.xlsx
+++ b/wiki/金融投資/台灣ETF比較清單.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="海外型" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'主動型'!$A$1:$H$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'主動型'!$A$1:$H$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'市值型'!$A$1:$I$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'高股息'!$A$1:$I$22</definedName>
   </definedNames>
@@ -1751,7 +1751,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H31"/>
+  <autoFilter ref="A1:H33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/wiki/金融投資/台灣ETF比較清單.xlsx
+++ b/wiki/金融投資/台灣ETF比較清單.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="新細明體"/>
       <family val="2"/>
@@ -47,13 +47,27 @@
       <sz val="9"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="新細明體"/>
+      <charset val="136"/>
+      <family val="1"/>
+      <color rgb="FF0563C1"/>
+      <sz val="11"/>
+      <u val="single"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -68,10 +82,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -440,12 +456,12 @@
   <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
-    <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="22.28515625" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="15.140625" bestFit="1" customWidth="1" min="3" max="4"/>
-    <col width="17.42578125" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="15" bestFit="1" customWidth="1" min="6" max="7"/>
-    <col width="15.140625" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="10.28515625" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
+    <col width="22.28515625" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
+    <col width="15.140625" bestFit="1" customWidth="1" style="4" min="3" max="4"/>
+    <col width="17.42578125" bestFit="1" customWidth="1" style="4" min="5" max="5"/>
+    <col width="15" bestFit="1" customWidth="1" style="4" min="6" max="7"/>
+    <col width="15.140625" bestFit="1" customWidth="1" style="4" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1753,6 +1769,7 @@
   </sheetData>
   <autoFilter ref="A1:H33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -1765,14 +1782,14 @@
   <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
-    <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="20" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="8.140625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="10.28515625" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="29.42578125" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="17.42578125" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="15" bestFit="1" customWidth="1" min="7" max="8"/>
-    <col width="15.140625" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="10.28515625" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
+    <col width="20" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
+    <col width="8.140625" bestFit="1" customWidth="1" style="4" min="3" max="3"/>
+    <col width="10.28515625" bestFit="1" customWidth="1" style="4" min="4" max="4"/>
+    <col width="29.42578125" bestFit="1" customWidth="1" style="4" min="5" max="5"/>
+    <col width="17.42578125" bestFit="1" customWidth="1" style="4" min="6" max="6"/>
+    <col width="15" bestFit="1" customWidth="1" style="4" min="7" max="8"/>
+    <col width="15.140625" bestFit="1" customWidth="1" style="4" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1865,7 +1882,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026/07/20</t>
+          <t>2026/07/21</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1929,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026/04/17</t>
+          <t>2026/04/20</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1976,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2025/10/22</t>
+          <t>2026/10/22</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2023,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026/07/15</t>
+          <t>2026/07/16</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2070,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026/07/15</t>
+          <t>2026/07/16</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2117,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026/04/17</t>
+          <t>2026/04/20</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2164,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026/05/21</t>
+          <t>2026/08/21</t>
         </is>
       </c>
     </row>
@@ -2194,7 +2211,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026/01/19</t>
+          <t>2026/08/18</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2258,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026/07/24</t>
+          <t>2026/07/27</t>
         </is>
       </c>
     </row>
@@ -2288,7 +2305,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026/07/15</t>
+          <t>2026/07/16</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2352,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026/07/15</t>
+          <t>2026/07/16</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2399,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026/02/26</t>
+          <t>2026/08/18</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2446,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
+          <t>2026/06/16</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2493,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026/03/16</t>
+          <t>2026/03/17</t>
         </is>
       </c>
     </row>
@@ -2521,9 +2538,9 @@
           <t>0.035%</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026/02/25</t>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2026/08/18</t>
         </is>
       </c>
     </row>
@@ -2570,7 +2587,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026/03/16</t>
+          <t>2026/03/17</t>
         </is>
       </c>
     </row>
@@ -2617,7 +2634,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026/07/14</t>
+          <t>2026/07/15</t>
         </is>
       </c>
     </row>
@@ -2799,14 +2816,14 @@
   <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
-    <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="24.7109375" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="10.28515625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="15.140625" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="31.85546875" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="22.28515625" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="15" bestFit="1" customWidth="1" min="7" max="8"/>
-    <col width="15.140625" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="10.28515625" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
+    <col width="24.7109375" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
+    <col width="10.28515625" bestFit="1" customWidth="1" style="4" min="3" max="3"/>
+    <col width="15.140625" bestFit="1" customWidth="1" style="4" min="4" max="4"/>
+    <col width="31.85546875" bestFit="1" customWidth="1" style="4" min="5" max="5"/>
+    <col width="22.28515625" bestFit="1" customWidth="1" style="4" min="6" max="6"/>
+    <col width="15" bestFit="1" customWidth="1" style="4" min="7" max="8"/>
+    <col width="15.140625" bestFit="1" customWidth="1" style="4" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2899,7 +2916,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026/07/20</t>
+          <t>2026/07/21</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2963,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026/01/19</t>
+          <t>2026/08/18</t>
         </is>
       </c>
     </row>
@@ -2993,7 +3010,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026/06/18</t>
+          <t>2026/06/22</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3057,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026/07/15</t>
+          <t>2026/08/18</t>
         </is>
       </c>
     </row>
@@ -3087,7 +3104,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026/05/19</t>
+          <t>2026/08/19</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3151,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026/05/18</t>
+          <t>2026/08/18</t>
         </is>
       </c>
     </row>
@@ -3181,7 +3198,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026/07/15</t>
+          <t>2026/08/18</t>
         </is>
       </c>
     </row>
@@ -3228,7 +3245,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026/06/23</t>
+          <t>2026/08/25</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3292,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
+          <t>2026/06/16</t>
         </is>
       </c>
     </row>
@@ -3322,7 +3339,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026/06/17</t>
+          <t>2026/06/18</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3386,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026/06/15</t>
+          <t>2026/06/16</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3433,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026/07/20</t>
+          <t>2026/08/19</t>
         </is>
       </c>
     </row>
@@ -3463,7 +3480,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026/07/24</t>
+          <t>2026/07/27</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3527,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026/07/15</t>
+          <t>2026/08/18</t>
         </is>
       </c>
     </row>
@@ -3557,7 +3574,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026/07/14</t>
+          <t>不配息</t>
         </is>
       </c>
     </row>
@@ -3604,7 +3621,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026/07/01</t>
+          <t>2026/07/02</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3668,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026/07/08</t>
+          <t>2026/08/11</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3715,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026/07/15</t>
+          <t>2026/08/18</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3762,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026/07/03</t>
+          <t>2026/08/04</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3809,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026/07/15</t>
+          <t>2026/08/18</t>
         </is>
       </c>
     </row>
@@ -3839,7 +3856,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026/07/15</t>
+          <t>2026/08/18</t>
         </is>
       </c>
     </row>
@@ -3881,12 +3898,12 @@
   <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
-    <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="18.7109375" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="30.42578125" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="8.140625" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="10.28515625" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="15" bestFit="1" customWidth="1" min="6" max="7"/>
+    <col width="10.28515625" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
+    <col width="18.7109375" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
+    <col width="30.42578125" bestFit="1" customWidth="1" style="4" min="3" max="3"/>
+    <col width="8.140625" bestFit="1" customWidth="1" style="4" min="4" max="4"/>
+    <col width="10.28515625" bestFit="1" customWidth="1" style="4" min="5" max="5"/>
+    <col width="15" bestFit="1" customWidth="1" style="4" min="6" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4357,17 +4374,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="15.75"/>
   <cols>
-    <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="29" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="33.85546875" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="8.140625" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="20" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="15.28515625" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="15" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="20.85546875" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="10.28515625" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
+    <col width="29" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
+    <col width="33.85546875" bestFit="1" customWidth="1" style="4" min="3" max="3"/>
+    <col width="8.140625" bestFit="1" customWidth="1" style="4" min="4" max="4"/>
+    <col width="20" bestFit="1" customWidth="1" style="4" min="5" max="5"/>
+    <col width="15.28515625" bestFit="1" customWidth="1" style="4" min="6" max="6"/>
+    <col width="15" bestFit="1" customWidth="1" style="4" min="7" max="7"/>
+    <col width="20.85546875" bestFit="1" customWidth="1" style="4" min="8" max="8"/>
+    <col width="15.140625" bestFit="1" customWidth="1" style="4" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4411,6 +4429,11 @@
           <t>保管費 (年率)</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>最近除息日期</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -4453,6 +4476,11 @@
           <t>0.06% (級距)</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>不配息</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -4495,6 +4523,11 @@
           <t>0.16%~0.21%</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>不配息</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -4537,6 +4570,11 @@
           <t>0.08%~0.16%</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026/06/17</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -4579,6 +4617,11 @@
           <t>0.18%</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>不配息</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -4621,6 +4664,11 @@
           <t>0.10%~0.15%</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026/01/20</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -4663,6 +4711,11 @@
           <t>0.06%~0.11%</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026/01/20</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -4705,6 +4758,11 @@
           <t>0.08%~0.15%</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>不配息</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -4747,6 +4805,11 @@
           <t>0.20%</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>不配息</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -4789,6 +4852,11 @@
           <t>0.06%~0.10% (級距)</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>尚未除息</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -4831,11 +4899,56 @@
           <t>0.06%~0.12% (級距)</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>尚未除息</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>009826</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>貝萊德iShares安碩世界股票</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>S&amp;P TIP世界股票指數</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>貝萊德</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>渣打銀行</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>不配息</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.40%~0.45%</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.10%~0.15%</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>不配息</t>
         </is>
       </c>
     </row>
@@ -4851,6 +4964,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/wiki/金融投資/台灣ETF比較清單.xlsx
+++ b/wiki/金融投資/台灣ETF比較清單.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="新細明體"/>
       <family val="2"/>
@@ -55,19 +55,19 @@
       <sz val="11"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="新細明體"/>
+      <color rgb="000563C1"/>
+      <sz val="11"/>
+      <u val="single"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -85,9 +85,13 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -456,12 +460,12 @@
   <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
-    <col width="10.28515625" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
-    <col width="22.28515625" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
-    <col width="15.140625" bestFit="1" customWidth="1" style="4" min="3" max="4"/>
-    <col width="17.42578125" bestFit="1" customWidth="1" style="4" min="5" max="5"/>
-    <col width="15" bestFit="1" customWidth="1" style="4" min="6" max="7"/>
-    <col width="15.140625" bestFit="1" customWidth="1" style="4" min="8" max="8"/>
+    <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="22.28515625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="15.140625" bestFit="1" customWidth="1" min="3" max="4"/>
+    <col width="17.42578125" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="15" bestFit="1" customWidth="1" min="6" max="7"/>
+    <col width="15.140625" bestFit="1" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -507,7 +511,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>00400A</t>
         </is>
@@ -549,7 +553,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>00401A</t>
         </is>
@@ -591,7 +595,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>00402A</t>
         </is>
@@ -633,7 +637,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>00403A</t>
         </is>
@@ -675,7 +679,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>00404A</t>
         </is>
@@ -717,7 +721,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>00405A</t>
         </is>
@@ -759,7 +763,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>00407A</t>
         </is>
@@ -801,7 +805,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>00408A</t>
         </is>
@@ -843,7 +847,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>00980A</t>
         </is>
@@ -885,7 +889,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>00981A</t>
         </is>
@@ -927,7 +931,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>00982A</t>
         </is>
@@ -969,7 +973,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>00983A</t>
         </is>
@@ -1011,7 +1015,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>00984A</t>
         </is>
@@ -1053,7 +1057,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>00985A</t>
         </is>
@@ -1095,7 +1099,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>00986A</t>
         </is>
@@ -1137,7 +1141,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>00987A</t>
         </is>
@@ -1179,7 +1183,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>00988A</t>
         </is>
@@ -1221,7 +1225,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>00989A</t>
         </is>
@@ -1263,7 +1267,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>00990A</t>
         </is>
@@ -1305,7 +1309,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>00991A</t>
         </is>
@@ -1347,7 +1351,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>00992A</t>
         </is>
@@ -1389,7 +1393,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>00993A</t>
         </is>
@@ -1431,7 +1435,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>00994A</t>
         </is>
@@ -1473,7 +1477,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>00995A</t>
         </is>
@@ -1515,7 +1519,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>00996A</t>
         </is>
@@ -1557,7 +1561,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>00997A</t>
         </is>
@@ -1599,7 +1603,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>00998A</t>
         </is>
@@ -1641,7 +1645,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>00999A</t>
         </is>
@@ -1683,7 +1687,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>00980D</t>
         </is>
@@ -1725,7 +1729,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>00983D</t>
         </is>
@@ -1768,6 +1772,38 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:H33"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
@@ -1779,17 +1815,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
-    <col width="10.28515625" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
-    <col width="20" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
-    <col width="8.140625" bestFit="1" customWidth="1" style="4" min="3" max="3"/>
-    <col width="10.28515625" bestFit="1" customWidth="1" style="4" min="4" max="4"/>
-    <col width="29.42578125" bestFit="1" customWidth="1" style="4" min="5" max="5"/>
-    <col width="17.42578125" bestFit="1" customWidth="1" style="4" min="6" max="6"/>
-    <col width="15" bestFit="1" customWidth="1" style="4" min="7" max="8"/>
-    <col width="15.140625" bestFit="1" customWidth="1" style="4" min="9" max="9"/>
+    <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="20" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="8.140625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="10.28515625" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="29.42578125" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="17.42578125" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="15" bestFit="1" customWidth="1" min="7" max="8"/>
+    <col width="15.140625" bestFit="1" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1840,7 +1876,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>0050</t>
         </is>
@@ -1887,7 +1923,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>0052</t>
         </is>
@@ -1934,7 +1970,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>006204</t>
         </is>
@@ -1981,7 +2017,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>006208</t>
         </is>
@@ -2028,7 +2064,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>00692</t>
         </is>
@@ -2075,7 +2111,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>00733</t>
         </is>
@@ -2122,7 +2158,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>00850</t>
         </is>
@@ -2169,7 +2205,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>00881</t>
         </is>
@@ -2216,7 +2252,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>00888</t>
         </is>
@@ -2263,7 +2299,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>00905</t>
         </is>
@@ -2310,7 +2346,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>00912</t>
         </is>
@@ -2357,7 +2393,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>00913</t>
         </is>
@@ -2404,7 +2440,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>00921</t>
         </is>
@@ -2451,7 +2487,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>00922</t>
         </is>
@@ -2498,7 +2534,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>00923</t>
         </is>
@@ -2538,14 +2574,14 @@
           <t>0.035%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>2026/08/18</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>00935</t>
         </is>
@@ -2592,7 +2628,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>00947</t>
         </is>
@@ -2639,7 +2675,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>009804</t>
         </is>
@@ -2686,7 +2722,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>009816</t>
         </is>
@@ -2727,53 +2763,6 @@
         </is>
       </c>
       <c r="I20" t="inlineStr">
-        <is>
-          <t>不配息</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>009821</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>野村全球稀土與關鍵資源</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>張怡琳</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>永豐商業銀行</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>NYSE TIP全球稀土與關鍵資源指數</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>不配息</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0.90%</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>0.20%</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
         <is>
           <t>不配息</t>
         </is>
@@ -2816,14 +2805,14 @@
   <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
-    <col width="10.28515625" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
-    <col width="24.7109375" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
-    <col width="10.28515625" bestFit="1" customWidth="1" style="4" min="3" max="3"/>
-    <col width="15.140625" bestFit="1" customWidth="1" style="4" min="4" max="4"/>
-    <col width="31.85546875" bestFit="1" customWidth="1" style="4" min="5" max="5"/>
-    <col width="22.28515625" bestFit="1" customWidth="1" style="4" min="6" max="6"/>
-    <col width="15" bestFit="1" customWidth="1" style="4" min="7" max="8"/>
-    <col width="15.140625" bestFit="1" customWidth="1" style="4" min="9" max="9"/>
+    <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="24.7109375" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="10.28515625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="15.140625" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="31.85546875" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="22.28515625" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="15" bestFit="1" customWidth="1" min="7" max="8"/>
+    <col width="15.140625" bestFit="1" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2874,7 +2863,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>0056</t>
         </is>
@@ -2921,7 +2910,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>00701</t>
         </is>
@@ -2968,7 +2957,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>00713</t>
         </is>
@@ -3015,7 +3004,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>00730</t>
         </is>
@@ -3062,7 +3051,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>00731</t>
         </is>
@@ -3109,7 +3098,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>00878</t>
         </is>
@@ -3156,7 +3145,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>00900</t>
         </is>
@@ -3203,7 +3192,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>00907</t>
         </is>
@@ -3250,7 +3239,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>00915</t>
         </is>
@@ -3297,7 +3286,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>00918</t>
         </is>
@@ -3344,7 +3333,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>00919</t>
         </is>
@@ -3391,7 +3380,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>00929</t>
         </is>
@@ -3438,7 +3427,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>00930</t>
         </is>
@@ -3485,7 +3474,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>00934</t>
         </is>
@@ -3532,7 +3521,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>00936</t>
         </is>
@@ -3579,7 +3568,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>00939</t>
         </is>
@@ -3626,7 +3615,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>00940</t>
         </is>
@@ -3673,7 +3662,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>00944</t>
         </is>
@@ -3720,7 +3709,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>00946</t>
         </is>
@@ -3767,7 +3756,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>00961</t>
         </is>
@@ -3814,7 +3803,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>00964</t>
         </is>
@@ -3898,12 +3887,12 @@
   <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
-    <col width="10.28515625" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
-    <col width="18.7109375" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
-    <col width="30.42578125" bestFit="1" customWidth="1" style="4" min="3" max="3"/>
-    <col width="8.140625" bestFit="1" customWidth="1" style="4" min="4" max="4"/>
-    <col width="10.28515625" bestFit="1" customWidth="1" style="4" min="5" max="5"/>
-    <col width="15" bestFit="1" customWidth="1" style="4" min="6" max="7"/>
+    <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="18.7109375" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="30.42578125" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="8.140625" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="10.28515625" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="15" bestFit="1" customWidth="1" min="6" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3944,7 +3933,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>00631L</t>
         </is>
@@ -3981,7 +3970,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>00632R</t>
         </is>
@@ -4018,7 +4007,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>00647L</t>
         </is>
@@ -4055,7 +4044,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>00648R</t>
         </is>
@@ -4092,7 +4081,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>00663L</t>
         </is>
@@ -4129,7 +4118,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>00664R</t>
         </is>
@@ -4166,7 +4155,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>00670L</t>
         </is>
@@ -4203,7 +4192,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>00671R</t>
         </is>
@@ -4240,7 +4229,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>00675L</t>
         </is>
@@ -4277,7 +4266,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>00685L</t>
         </is>
@@ -4314,7 +4303,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>00686R</t>
         </is>
@@ -4374,18 +4363,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5703125" defaultRowHeight="15.75"/>
   <cols>
-    <col width="10.28515625" bestFit="1" customWidth="1" style="4" min="1" max="1"/>
-    <col width="29" bestFit="1" customWidth="1" style="4" min="2" max="2"/>
-    <col width="33.85546875" bestFit="1" customWidth="1" style="4" min="3" max="3"/>
-    <col width="8.140625" bestFit="1" customWidth="1" style="4" min="4" max="4"/>
-    <col width="20" bestFit="1" customWidth="1" style="4" min="5" max="5"/>
-    <col width="15.28515625" bestFit="1" customWidth="1" style="4" min="6" max="6"/>
-    <col width="15" bestFit="1" customWidth="1" style="4" min="7" max="7"/>
-    <col width="20.85546875" bestFit="1" customWidth="1" style="4" min="8" max="8"/>
-    <col width="15.140625" bestFit="1" customWidth="1" style="4" min="9" max="9"/>
+    <col width="10.28515625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="29" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="33.85546875" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="8.140625" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="20" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="15.28515625" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="15" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="20.85546875" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="15.140625" bestFit="1" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4436,7 +4425,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>00646</t>
         </is>
@@ -4483,7 +4472,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>00662</t>
         </is>
@@ -4530,7 +4519,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>00712</t>
         </is>
@@ -4577,7 +4566,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>00757</t>
         </is>
@@ -4624,7 +4613,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>00770</t>
         </is>
@@ -4671,7 +4660,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>00830</t>
         </is>
@@ -4718,7 +4707,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>00924</t>
         </is>
@@ -4765,7 +4754,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>00941</t>
         </is>
@@ -4812,91 +4801,91 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>009821</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>野村全球稀土與關鍵資源</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>張怡琳</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>永豐商業銀行</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>NYSE TIP全球稀土與關鍵資源指數</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>不配息</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.90%</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.20%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>不配息</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>009823</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>群益標普500 ETF</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>標普 500 指數（S&amp;P 500 Index）</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>謝明志</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>華南銀行</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>季配 (2,5,8,11)</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>0.20% (級距)</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>0.06%~0.10% (級距)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>尚未除息</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>009824</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>群益美國科技巨頭ETF基金</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Solactive美國科技巨頭指數</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>李晉含</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>中國信託商業銀行</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>季配 (3,6,9,12)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0.80%</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.06%~0.12% (級距)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4908,45 +4897,92 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
+          <t>009824</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>群益美國科技巨頭ETF基金</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Solactive美國科技巨頭指數</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>李晉含</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>中國信託商業銀行</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>季配 (3,6,9,12)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.80%</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.06%~0.12% (級距)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>尚未除息</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
           <t>009826</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>貝萊德iShares安碩世界股票</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>S&amp;P TIP世界股票指數</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>貝萊德</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>渣打銀行</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>不配息</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>0.40%~0.45%</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>0.10%~0.15%</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>不配息</t>
         </is>
@@ -4965,6 +5001,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/wiki/金融投資/台灣ETF比較清單.xlsx
+++ b/wiki/金融投資/台灣ETF比較清單.xlsx
@@ -511,7 +511,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>00400A</t>
         </is>
@@ -553,7 +553,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>00401A</t>
         </is>
@@ -595,7 +595,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>00402A</t>
         </is>
@@ -637,7 +637,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>00403A</t>
         </is>
@@ -679,7 +679,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>00404A</t>
         </is>
@@ -721,7 +721,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>00405A</t>
         </is>
@@ -763,7 +763,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>00407A</t>
         </is>
@@ -805,7 +805,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>00408A</t>
         </is>
@@ -847,7 +847,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>00980A</t>
         </is>
@@ -889,7 +889,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>00981A</t>
         </is>
@@ -931,7 +931,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>00982A</t>
         </is>
@@ -973,7 +973,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>00983A</t>
         </is>
@@ -1015,7 +1015,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>00984A</t>
         </is>
@@ -1057,7 +1057,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>00985A</t>
         </is>
@@ -1099,7 +1099,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>00986A</t>
         </is>
@@ -1141,7 +1141,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>00987A</t>
         </is>
@@ -1183,7 +1183,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>00988A</t>
         </is>
@@ -1225,7 +1225,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>00989A</t>
         </is>
@@ -1267,7 +1267,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>00990A</t>
         </is>
@@ -1309,7 +1309,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>00991A</t>
         </is>
@@ -1351,7 +1351,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>00992A</t>
         </is>
@@ -1393,7 +1393,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>00993A</t>
         </is>
@@ -1435,7 +1435,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>00994A</t>
         </is>
@@ -1477,7 +1477,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>00995A</t>
         </is>
@@ -1519,7 +1519,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>00996A</t>
         </is>
@@ -1561,7 +1561,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>00997A</t>
         </is>
@@ -1603,7 +1603,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>00998A</t>
         </is>
@@ -1645,7 +1645,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>00999A</t>
         </is>
@@ -1687,7 +1687,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>00980D</t>
         </is>
@@ -1729,7 +1729,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>00983D</t>
         </is>
@@ -1772,38 +1772,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:H33"/>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId30"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>

--- a/wiki/金融投資/台灣ETF比較清單.xlsx
+++ b/wiki/金融投資/台灣ETF比較清單.xlsx
@@ -24,21 +24,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="新細明體"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="新細明體"/>
-      <charset val="136"/>
-      <family val="1"/>
-      <color rgb="FF0563C1"/>
-      <sz val="11"/>
-      <u val="single"/>
     </font>
     <font>
       <name val="新細明體"/>
@@ -57,7 +49,9 @@
     </font>
     <font>
       <name val="新細明體"/>
-      <color rgb="000563C1"/>
+      <charset val="136"/>
+      <family val="1"/>
+      <color rgb="FF0563C1"/>
       <sz val="11"/>
       <u val="single"/>
     </font>
@@ -82,16 +76,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="1" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1844,7 +1837,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>0050</t>
         </is>
@@ -1891,7 +1884,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>0052</t>
         </is>
@@ -1938,7 +1931,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>006204</t>
         </is>
@@ -1985,7 +1978,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>006208</t>
         </is>
@@ -2032,7 +2025,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>00692</t>
         </is>
@@ -2079,7 +2072,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>00733</t>
         </is>
@@ -2126,7 +2119,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>00850</t>
         </is>
@@ -2173,7 +2166,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>00881</t>
         </is>
@@ -2220,7 +2213,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>00888</t>
         </is>
@@ -2267,7 +2260,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>00905</t>
         </is>
@@ -2314,7 +2307,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>00912</t>
         </is>
@@ -2361,7 +2354,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>00913</t>
         </is>
@@ -2408,7 +2401,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>00921</t>
         </is>
@@ -2455,7 +2448,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>00922</t>
         </is>
@@ -2502,7 +2495,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>00923</t>
         </is>
@@ -2549,7 +2542,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>00935</t>
         </is>
@@ -2596,7 +2589,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>00947</t>
         </is>
@@ -2643,7 +2636,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>009804</t>
         </is>
@@ -2690,7 +2683,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>009816</t>
         </is>
@@ -2831,7 +2824,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>0056</t>
         </is>
@@ -2878,7 +2871,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>00701</t>
         </is>
@@ -2925,7 +2918,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>00713</t>
         </is>
@@ -2972,7 +2965,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>00730</t>
         </is>
@@ -3019,7 +3012,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>00731</t>
         </is>
@@ -3066,7 +3059,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>00878</t>
         </is>
@@ -3113,7 +3106,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>00900</t>
         </is>
@@ -3160,7 +3153,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>00907</t>
         </is>
@@ -3207,7 +3200,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>00915</t>
         </is>
@@ -3254,7 +3247,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>00918</t>
         </is>
@@ -3301,7 +3294,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>00919</t>
         </is>
@@ -3348,7 +3341,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>00929</t>
         </is>
@@ -3395,7 +3388,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>00930</t>
         </is>
@@ -3442,7 +3435,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>00934</t>
         </is>
@@ -3489,7 +3482,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>00936</t>
         </is>
@@ -3536,7 +3529,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>00939</t>
         </is>
@@ -3583,7 +3576,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>00940</t>
         </is>
@@ -3630,7 +3623,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>00944</t>
         </is>
@@ -3677,7 +3670,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>00946</t>
         </is>
@@ -3724,7 +3717,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>00961</t>
         </is>
@@ -3771,7 +3764,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>00964</t>
         </is>
@@ -3901,7 +3894,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>00631L</t>
         </is>
@@ -3938,7 +3931,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>00632R</t>
         </is>
@@ -3975,7 +3968,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>00647L</t>
         </is>
@@ -4012,7 +4005,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>00648R</t>
         </is>
@@ -4049,7 +4042,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>00663L</t>
         </is>
@@ -4086,7 +4079,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>00664R</t>
         </is>
@@ -4123,7 +4116,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>00670L</t>
         </is>
@@ -4160,7 +4153,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>00671R</t>
         </is>
@@ -4197,7 +4190,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>00675L</t>
         </is>
@@ -4234,7 +4227,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>00685L</t>
         </is>
@@ -4271,7 +4264,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>00686R</t>
         </is>
@@ -4393,7 +4386,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>00646</t>
         </is>
@@ -4440,7 +4433,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>00662</t>
         </is>
@@ -4487,7 +4480,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>00712</t>
         </is>
@@ -4534,7 +4527,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>00757</t>
         </is>
@@ -4581,7 +4574,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>00770</t>
         </is>
@@ -4628,7 +4621,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>00830</t>
         </is>
@@ -4675,7 +4668,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>00924</t>
         </is>
@@ -4722,7 +4715,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>00941</t>
         </is>
@@ -4769,7 +4762,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>009821</t>
         </is>
@@ -4816,7 +4809,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>009823</t>
         </is>
@@ -4863,7 +4856,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>009824</t>
         </is>
@@ -4910,7 +4903,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>009826</t>
         </is>
